--- a/workbook/heart_toolkit.xlsx
+++ b/workbook/heart_toolkit.xlsx
@@ -865,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA104"/>
+  <dimension ref="A1:AA105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="44" min="1" max="1"/>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="B94" s="54" t="inlineStr">
         <is>
-          <t>Converse (2024)</t>
+          <t>ConVerse (Findings of EACL 2026)</t>
         </is>
       </c>
       <c r="C94" s="54" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="E94" s="54" t="inlineStr">
         <is>
-          <t>Contextual Integrity (CI)-driven vignette templating framework</t>
+          <t>Agent-to-agent contextual safety benchmark with three-tier privacy taxonomy — spans travel, real estate, and insurance with 12 user personas and 864 contextually grounded attacks (611 privacy + 253 security); models autonomous multi-turn agent-to-agent dialogues where malicious requests are embedded within plausible discourse.</t>
         </is>
       </c>
       <c r="F94" s="54" t="inlineStr">
@@ -11410,12 +11410,12 @@
       </c>
       <c r="B95" s="54" t="inlineStr">
         <is>
-          <t>EAI-Bench (2024)</t>
+          <t>EAPrivacy (ICLR 2026)</t>
         </is>
       </c>
       <c r="C95" s="54" t="inlineStr">
         <is>
-          <t>EAI-Bench</t>
+          <t>EAPrivacy</t>
         </is>
       </c>
       <c r="D95" s="54" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="E95" s="54" t="inlineStr">
         <is>
-          <t>Tiered physical-object privacy sensitivity ladder</t>
+          <t>Four-tier physical-world privacy benchmark for embodied LLM agents with 400+ procedurally generated scenarios across Sensitive Object Identification, Privacy in Shifting Environments, Inferential Privacy under Task Conflicts, and Social Norms vs Personal Privacy; supports both rating and triplet selection evaluations validated against human raters.</t>
         </is>
       </c>
       <c r="F95" s="54" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="E96" s="54" t="inlineStr">
         <is>
-          <t>Law-grounded contextual integrity question generation pipeline</t>
+          <t>Law-grounded contextual integrity question generation pipeline anchored to HIPAA Privacy Rule §164.502 — releases GoldCoin-HIPAA with 309 synthetic compliance/violation cases generated from CI-tagged statutes plus 107 Caselaw Access Project (CAP) real court cases (and 107 unrelated cases) for the compliance and applicability tasks.</t>
         </is>
       </c>
       <c r="F96" s="54" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="E97" s="54" t="inlineStr">
         <is>
-          <t>Contextual Integrity 5-tuple agent trajectory tester</t>
+          <t>Seed → vignette → agent trajectory pipeline that extends crowdsourced privacy-sensitive seeds (grounded in privacy literature) into expressive vignettes and then into LM agent action trajectories; reports two-level metrics: probing-question accuracy (norm awareness) vs. action-leakage / helpfulness in executed trajectories, revealing a discrepancy between answering and acting.</t>
         </is>
       </c>
       <c r="F97" s="54" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="B98" s="54" t="inlineStr">
         <is>
-          <t>WebArena-Privacy (2024)</t>
+          <t>AgentDAM (2025)</t>
         </is>
       </c>
       <c r="C98" s="54" t="inlineStr">
         <is>
-          <t>WebArena-Privacy</t>
+          <t>AgentDAM</t>
         </is>
       </c>
       <c r="D98" s="54" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="E98" s="54" t="inlineStr">
         <is>
-          <t>Web-based privacy decision sandbox with PII-contaminated intent injection</t>
+          <t>Web-based privacy leakage evaluation for autonomous web agents — measures whether a multi-step web-navigation agent adheres to data-minimization when handling user data during agentic tasks, built on the WebArena environment with PII-contaminated intent injection across 246 task variants.</t>
         </is>
       </c>
       <c r="F98" s="54" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="E104" s="54" t="inlineStr">
         <is>
-          <t>Privacy-Boundary Entailment (PBE) scorer — semantic entailment framework for information flow control</t>
+          <t>Comprehensive privacy-evaluation toolkit for LLMs spanning the full lifecycle (pre-training → fine-tuning → in-context inference), covering multiple attack families (training-data extraction, membership inference, jailbreak-style privacy probes), defenses (DP-SGD, scrubbing, DP-ICL), data types (free-text PII, structured PII, contextual social info), and standardized metrics — toolkit-style benchmark rather than a single scoring rubric.</t>
         </is>
       </c>
       <c r="F104" s="54" t="inlineStr">
@@ -12382,6 +12382,44 @@
       <c r="AA104" s="54" t="inlineStr">
         <is>
           <t>综述指出，LLM-PBE [Li et al., 2024b] 使用语义匹配和推理分数来评估信息流控制。早期基准依赖于静态的单轮句子补全（完形填空测试）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MPCI-Bench (2026)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MPCI-Bench</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>First multimodal pairwise contextual-integrity benchmark for LM agents — paired positive/negative instances derived from the same visual source, instantiated across three tiers (normative Seed judgments, context-rich Story reasoning, and executable agent action Traces) via a Tri-Principle Iterative Refinement pipeline; explicitly surfaces a modality-leakage gap where sensitive visual information leaks more frequently than equivalent textual information.</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Existing CI benchmarks are largely text-centric and primarily emphasize negative refusal scenarios; MPCI-Bench fills that gap by being multimodal, by using paired positive/negative instances tied to the same visual source (so privacy–utility trade-offs are explicit), and by reaching all the way to executable agent action traces rather than stopping at norm judgments.</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Authors note that current state-of-the-art multimodal models systematically fail to balance privacy and utility, and that modality leakage requires further investigation; coverage of social/cultural CI norms is bounded by the underlying visual sources.</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>与已有 CI benchmark（PrivaCI-Bench、ConfAIde、PrivacyLens）相比，MPCI-Bench 把评测从纯文本扩展到多模态，强制要求模型在同一视觉来源上做正/负对比，并把评测链路从"判断"延伸到"执行"，揭示了模态间的泄露不对称性。</t>
         </is>
       </c>
     </row>
@@ -23414,8 +23452,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
     <row r="95" s="44"/>
     <row r="96" ht="125" customHeight="1" s="44">
       <c r="A96" s="54" t="n"/>
@@ -26957,8 +26993,6 @@
         </is>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131"/>
     <row r="132" s="44"/>
     <row r="133" ht="125" customHeight="1" s="44">
       <c r="A133" s="54" t="n"/>
